--- a/backend/app/data/controls/PMS_Controls_Self_Certified_RE.xlsx
+++ b/backend/app/data/controls/PMS_Controls_Self_Certified_RE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9C9FC3-1DD4-48FF-8D7D-7263B9468CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDECE3B6-30AD-4DAB-BCA9-08712CE988F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-106" yWindow="-106" windowWidth="18644" windowHeight="9879" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="97">
   <si>
     <t>S.No</t>
   </si>
@@ -301,6 +301,24 @@
   </si>
   <si>
     <t>Post-change VAPT/Delta testing report certificates</t>
+  </si>
+  <si>
+    <t>Audit_framework</t>
+  </si>
+  <si>
+    <t>Audit_category</t>
+  </si>
+  <si>
+    <t>Audit_subcategory</t>
+  </si>
+  <si>
+    <t>PMS</t>
+  </si>
+  <si>
+    <t>self_certified</t>
+  </si>
+  <si>
+    <t>SEBI-CSCRF</t>
   </si>
 </sst>
 </file>
@@ -320,12 +338,12 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -369,13 +387,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -641,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -650,10 +674,12 @@
     <col min="4" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="8" max="8" width="45" customWidth="1"/>
+    <col min="7" max="7" width="15.9140625" customWidth="1"/>
+    <col min="8" max="8" width="25.25" customWidth="1"/>
+    <col min="9" max="9" width="23.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="38.9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="38.9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -672,9 +698,17 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" ht="69.150000000000006" x14ac:dyDescent="0.35">
+      <c r="G1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="69.150000000000006" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -693,9 +727,17 @@
       <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" ht="34.6" x14ac:dyDescent="0.35">
+      <c r="G2" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="46.1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -714,9 +756,17 @@
       <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" ht="34.6" x14ac:dyDescent="0.35">
+      <c r="G3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="34.6" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -733,9 +783,17 @@
         <v>17</v>
       </c>
       <c r="F4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" ht="34.6" x14ac:dyDescent="0.35">
+      <c r="G4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="34.6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -754,9 +812,17 @@
       <c r="F5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" ht="46.1" x14ac:dyDescent="0.35">
+      <c r="G5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="46.1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -775,9 +841,17 @@
       <c r="F6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" ht="46.1" x14ac:dyDescent="0.35">
+      <c r="G6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="46.1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -796,9 +870,17 @@
       <c r="F7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" ht="34.6" x14ac:dyDescent="0.35">
+      <c r="G7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="34.6" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -817,9 +899,17 @@
       <c r="F8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" ht="34.6" x14ac:dyDescent="0.35">
+      <c r="G8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="34.6" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -838,9 +928,17 @@
       <c r="F9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" ht="34.6" x14ac:dyDescent="0.35">
+      <c r="G9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="34.6" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -859,9 +957,17 @@
       <c r="F10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" ht="46.1" x14ac:dyDescent="0.35">
+      <c r="G10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="46.1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -880,9 +986,17 @@
       <c r="F11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" ht="46.1" x14ac:dyDescent="0.35">
+      <c r="G11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="46.1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -901,9 +1015,17 @@
       <c r="F12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" ht="46.1" x14ac:dyDescent="0.35">
+      <c r="G12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="46.1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -922,9 +1044,17 @@
       <c r="F13" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" ht="23.05" x14ac:dyDescent="0.35">
+      <c r="G13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="23.05" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -943,9 +1073,17 @@
       <c r="F14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" ht="34.6" x14ac:dyDescent="0.35">
+      <c r="G14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="34.6" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -964,9 +1102,17 @@
       <c r="F15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" ht="34.6" x14ac:dyDescent="0.35">
+      <c r="G15" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="34.6" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -985,9 +1131,17 @@
       <c r="F16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" ht="34.6" x14ac:dyDescent="0.35">
+      <c r="G16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="34.6" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1006,9 +1160,17 @@
       <c r="F17" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" ht="34.6" x14ac:dyDescent="0.35">
+      <c r="G17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="34.6" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1027,9 +1189,17 @@
       <c r="F18" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" ht="34.6" x14ac:dyDescent="0.35">
+      <c r="G18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="34.6" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1048,9 +1218,17 @@
       <c r="F19" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" ht="34.6" x14ac:dyDescent="0.35">
+      <c r="G19" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="34.6" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1069,9 +1247,17 @@
       <c r="F20" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="1:8" ht="34.6" x14ac:dyDescent="0.35">
+      <c r="G20" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="34.6" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1090,7 +1276,15 @@
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H21" s="2"/>
+      <c r="G21" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>95</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
